--- a/data/Data Dictionary.xlsx
+++ b/data/Data Dictionary.xlsx
@@ -5,19 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a2635ae937cd6fcd/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adity\OneDrive\Documents\GitHub\NFL-Big-Data-Bowl-2027\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9931B4A-1741-4167-A882-89C5383AF0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ED8671-220A-41E9-92C6-78E31B22A9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{44132284-F98A-4360-918D-FDB67CB14041}"/>
+    <workbookView xWindow="-19110" yWindow="1260" windowWidth="19200" windowHeight="10170" firstSheet="4" activeTab="6" xr2:uid="{44132284-F98A-4360-918D-FDB67CB14041}"/>
   </bookViews>
   <sheets>
-    <sheet name="players.csv" sheetId="1" r:id="rId1"/>
-    <sheet name="combine_results.csv" sheetId="2" r:id="rId2"/>
-    <sheet name="combine_tracking.csv" sheetId="3" r:id="rId3"/>
-    <sheet name="player_career_successes.csv" sheetId="4" r:id="rId4"/>
-    <sheet name="player_play.csv" sheetId="5" r:id="rId5"/>
+    <sheet name="1. players.csv" sheetId="1" r:id="rId1"/>
+    <sheet name="2. combine_results.csv" sheetId="2" r:id="rId2"/>
+    <sheet name="3. combine_tracking.csv" sheetId="3" r:id="rId3"/>
+    <sheet name="4. player_career_successes.csv" sheetId="4" r:id="rId4"/>
+    <sheet name="5. player_play.csv" sheetId="5" r:id="rId5"/>
+    <sheet name="6. games.csv" sheetId="6" r:id="rId6"/>
+    <sheet name="7,8,9. game_tracking_2023,24,25" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="302">
   <si>
     <t>Column Name</t>
   </si>
@@ -506,13 +508,442 @@
   </si>
   <si>
     <t>Direction of offensive play progression (left or right).</t>
+  </si>
+  <si>
+    <t>A. Play Context &amp; Identifiers</t>
+  </si>
+  <si>
+    <t>B. Win Probability &amp; Expected Points</t>
+  </si>
+  <si>
+    <t>pre_snap_home_team_win_probability</t>
+  </si>
+  <si>
+    <t>Home team estimated win probability prior to snap.</t>
+  </si>
+  <si>
+    <t>pre_snap_visitor_team_win_probability</t>
+  </si>
+  <si>
+    <t>Visiting team estimated win probability prior to snap.</t>
+  </si>
+  <si>
+    <t>home_team_win_probability_added</t>
+  </si>
+  <si>
+    <t>Change in home team win probability produced by the play.</t>
+  </si>
+  <si>
+    <t>visitor_team_win_probility_added</t>
+  </si>
+  <si>
+    <t>Change in visiting team win probability produced by the play.</t>
+  </si>
+  <si>
+    <t>expected_points_added</t>
+  </si>
+  <si>
+    <t>Net Expected Points Added (EPA) generated on the play.</t>
+  </si>
+  <si>
+    <t>expected_points</t>
+  </si>
+  <si>
+    <t>Expected points value of the offensive drive state prior to snap.</t>
+  </si>
+  <si>
+    <t>C. Schemes, Formations &amp; Play Results</t>
+  </si>
+  <si>
+    <t>offense_formation</t>
+  </si>
+  <si>
+    <t>EMPTY</t>
+  </si>
+  <si>
+    <t>receiver_alignment</t>
+  </si>
+  <si>
+    <t>3x2</t>
+  </si>
+  <si>
+    <t>pass_result</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>pass_length</t>
+  </si>
+  <si>
+    <t>Air yards traveled by the pass past the line of scrimmage (negative for passes behind the LOS).</t>
+  </si>
+  <si>
+    <t>play_nullified_by_penalty</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>penalty_yards</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Total penalty yardage enforced on the play.</t>
+  </si>
+  <si>
+    <t>pre_penalty_yards_gained</t>
+  </si>
+  <si>
+    <t>Gross yards gained before penalty assessment.</t>
+  </si>
+  <si>
+    <t>yards_gained</t>
+  </si>
+  <si>
+    <t>Official net yards gained on the play.</t>
+  </si>
+  <si>
+    <t>team_coverage_man_zone</t>
+  </si>
+  <si>
+    <t>ZONE_COVERAGE</t>
+  </si>
+  <si>
+    <t>team_coverage_type</t>
+  </si>
+  <si>
+    <t>COVER_6_ZONE</t>
+  </si>
+  <si>
+    <t>in_motion_at_ball_snap</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>True if the player was in active pre-snap motion when the ball was snapped.</t>
+  </si>
+  <si>
+    <t>Offensive pre-snap personnel formation (e.g., SHOTGUN, SINGLEBACK, EMPTY, I_FORM, PISTOL, JUMBO).</t>
+  </si>
+  <si>
+    <t>Wide receiver alignment distribution (e.g., 3x1, 2x2, 3x2, 1x1, 4x1).</t>
+  </si>
+  <si>
+    <t>Outcome of the pass play: C (Complete), I (Incomplete), S (Sack), IN (Interception), R (Scramble).</t>
+  </si>
+  <si>
+    <t>Y if the play outcome was wiped out by penalty, N otherwise.</t>
+  </si>
+  <si>
+    <t>Primary defensive coverage scheme classification (MAN_COVERAGE, ZONE_COVERAGE).</t>
+  </si>
+  <si>
+    <t>Specific defensive coverage shell (e.g., COVER_1, COVER_2, COVER_3, COVER_4, COVER_6_ZONE, COVER_0, PREVENT).</t>
+  </si>
+  <si>
+    <t>D. Receiver &amp; Ball Carrier Metrics</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>True if the player was the intended target of the pass.</t>
+  </si>
+  <si>
+    <t>rec_yards</t>
+  </si>
+  <si>
+    <t>Receiving yards gained by the player on the play.</t>
+  </si>
+  <si>
+    <t>rush_yards</t>
+  </si>
+  <si>
+    <t>Rushing yards gained by the player on the play.</t>
+  </si>
+  <si>
+    <t>yards_after_catch</t>
+  </si>
+  <si>
+    <t>Yards gained by the receiver after securing the catch (YAC).</t>
+  </si>
+  <si>
+    <t>fumble</t>
+  </si>
+  <si>
+    <t>fumble_lost</t>
+  </si>
+  <si>
+    <t>route_ran</t>
+  </si>
+  <si>
+    <t>SLANT</t>
+  </si>
+  <si>
+    <t>separation_at_pass_forward</t>
+  </si>
+  <si>
+    <t>Distance in yards to the nearest defender at the moment the ball is thrown forward.</t>
+  </si>
+  <si>
+    <t>cushion</t>
+  </si>
+  <si>
+    <t>Pre-snap distance in yards between the receiver and their primary coverage defender.</t>
+  </si>
+  <si>
+    <t>expected_yards_after_catch</t>
+  </si>
+  <si>
+    <t>Next Gen Stats expected yards after catch model prediction at catch moment.</t>
+  </si>
+  <si>
+    <t>1.0 if the player fumbled the ball on the play, 0.0 otherwise.</t>
+  </si>
+  <si>
+    <t>1.0 if the player's fumble was recovered by the opponent.</t>
+  </si>
+  <si>
+    <t>Specific route run by the receiver (e.g., GO, OUT, SLANT, CROSS, POST, CORNER, HITCH, SCREEN, FLAT, WHEEL).</t>
+  </si>
+  <si>
+    <t>E. Offensive Line &amp; Pass Protection Metrics</t>
+  </si>
+  <si>
+    <t>dropback_duration</t>
+  </si>
+  <si>
+    <t>Time from snap to pass release, sack, or pressure in seconds.</t>
+  </si>
+  <si>
+    <t>extended_sack_allowed</t>
+  </si>
+  <si>
+    <t>Sacks allowed on extended dropbacks exceeding 4.0 seconds.</t>
+  </si>
+  <si>
+    <t>pass_rushers_encountered</t>
+  </si>
+  <si>
+    <t>Number of distinct pass rushers engaged by the offensive lineman on the play.</t>
+  </si>
+  <si>
+    <t>peak_pressure_probability_allowed</t>
+  </si>
+  <si>
+    <t>Peak estimated pressure probability allowed by the offensive lineman.</t>
+  </si>
+  <si>
+    <t>pressure_allowed</t>
+  </si>
+  <si>
+    <t>True if the offensive lineman allowed a pressure (QB hurry, hit, or sack).</t>
+  </si>
+  <si>
+    <t>sack_allowed</t>
+  </si>
+  <si>
+    <t>Sacks charged to the offensive lineman (1.0 for solo, 0.5 for shared).</t>
+  </si>
+  <si>
+    <t>time_to_pressure_allowed</t>
+  </si>
+  <si>
+    <t>Time in seconds from snap until the offensive lineman allowed pressure.</t>
+  </si>
+  <si>
+    <t>F. Defensive Pass Rush &amp; Tackle Metrics</t>
+  </si>
+  <si>
+    <t>blitzing</t>
+  </si>
+  <si>
+    <t>True if the defender was rushing the passer on a blitz.</t>
+  </si>
+  <si>
+    <t>player_get_off</t>
+  </si>
+  <si>
+    <t>Time in seconds from ball snap until defensive rusher moves forward across the line of scrimmage.</t>
+  </si>
+  <si>
+    <t>sack</t>
+  </si>
+  <si>
+    <t>tackle</t>
+  </si>
+  <si>
+    <t>assist</t>
+  </si>
+  <si>
+    <t>caused_forced_fumble</t>
+  </si>
+  <si>
+    <t>recovered_fumble</t>
+  </si>
+  <si>
+    <t>tackle_for_loss</t>
+  </si>
+  <si>
+    <t>time_to_pressure</t>
+  </si>
+  <si>
+    <t>Time elapsed from snap until this defender generated pressure on the quarterback.</t>
+  </si>
+  <si>
+    <t>time_to_qb_hurry</t>
+  </si>
+  <si>
+    <t>Time elapsed from snap until this defender forced a QB hurry.</t>
+  </si>
+  <si>
+    <t>coverage_assignment</t>
+  </si>
+  <si>
+    <t>MAN</t>
+  </si>
+  <si>
+    <t>coverage_assignment_at_snap</t>
+  </si>
+  <si>
+    <t>Coverage responsibility updated at ball snap following pre-snap motion.</t>
+  </si>
+  <si>
+    <t>quick_pressure</t>
+  </si>
+  <si>
+    <t>unblocked_pressure</t>
+  </si>
+  <si>
+    <t>1.0 if the defender recorded a sack on the play (0.5 for shared sack).</t>
+  </si>
+  <si>
+    <t>1.0 if the defender made a solo tackle on the ball carrier.</t>
+  </si>
+  <si>
+    <t>1.0 if the defender assisted on a tackle.</t>
+  </si>
+  <si>
+    <t>1.0 if the defender forced a fumble on the play.</t>
+  </si>
+  <si>
+    <t>1.0 if the player recovered a loose fumble.</t>
+  </si>
+  <si>
+    <t>1.0 if the tackle stopped the play behind the line of scrimmage for negative yards.</t>
+  </si>
+  <si>
+    <t>Pre-snap coverage assignment (e.g., MAN, DEEP_THIRD, FLAT, HOOK_CURL).</t>
+  </si>
+  <si>
+    <t>1.0 if a pass rusher pressures within 2.50 seconds of the snap.</t>
+  </si>
+  <si>
+    <t>1.0 if a pass rusher pressured the QB through this lineman's gap without being blocked.</t>
+  </si>
+  <si>
+    <t>Contains schedule, season, and team matchup metadata for all 1,002 NFL regular-season and playoff games across 2023, 2024, and 2025.</t>
+  </si>
+  <si>
+    <t>File name: games.csv</t>
+  </si>
+  <si>
+    <t>game_key</t>
+  </si>
+  <si>
+    <t>Historical NFL game key identifier.</t>
+  </si>
+  <si>
+    <t>season</t>
+  </si>
+  <si>
+    <t>season_type</t>
+  </si>
+  <si>
+    <t>REG</t>
+  </si>
+  <si>
+    <t>week</t>
+  </si>
+  <si>
+    <t>Week number within the season (Weeks 1–18).</t>
+  </si>
+  <si>
+    <t>home_team_abbr</t>
+  </si>
+  <si>
+    <t>KC</t>
+  </si>
+  <si>
+    <t>3-letter abbreviation of the home team.</t>
+  </si>
+  <si>
+    <t>visitor_team_abbr</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>3-letter abbreviation of the visiting team.</t>
+  </si>
+  <si>
+    <t>Unique 10-digit NFL game identifier (YYYYMMDD##). Primary key.</t>
+  </si>
+  <si>
+    <t>NFL season year (2023, 2024, 2025).</t>
+  </si>
+  <si>
+    <t>Type of season: REG (Regular Season) or POST (Playoffs).</t>
+  </si>
+  <si>
+    <t>Contain 10 Hz high-frequency in-game optical tracking frames for all rookie cohort prospects across each respective NFL season.</t>
+  </si>
+  <si>
+    <t>2024-08-10T01:30:31.800</t>
+  </si>
+  <si>
+    <t>ISO 8601 timestamp for the in-game optical tracking frame (sampled every 0.10s).</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>Player body orientation angle in degrees (0-360).</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>pass_forward</t>
+  </si>
+  <si>
+    <t>Game identifier matching games.csv.</t>
+  </si>
+  <si>
+    <t>Play identifier matching player_play.csv.</t>
+  </si>
+  <si>
+    <t>Player identifier matching players.csv (tracks all 510 rookie cohort prospects).</t>
+  </si>
+  <si>
+    <t>str / null</t>
+  </si>
+  <si>
+    <t>Game play milestone event tag (e.g., ball_snap, pass_forward, pass_arrived, tackle, touchdown, first_contact, out_of_bounds, or null for regular frames).</t>
+  </si>
+  <si>
+    <t>File name: game_tracking_2023/2024/2025.csv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -571,6 +1002,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -607,27 +1053,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -636,24 +1067,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -661,17 +1082,55 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,6 +1147,138 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>317501</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>236091</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>218811</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>309424</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Figure 1: Field coordinates, direction, and orientation">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CCE0F64-4932-414E-A7B6-E29B9107ABDE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7261796" y="5120706"/>
+          <a:ext cx="7228233" cy="4046154"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>10767</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>223454</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Figure 1: Field coordinates, direction, and orientation">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{971A8C67-F651-D627-BB71-1B76DDC40EE7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5586067" y="749300"/>
+          <a:ext cx="7228233" cy="4046154"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -997,178 +1588,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="50" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="9">
         <v>55867</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="9">
         <v>2023</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="50" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="26">
         <v>37136</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="50" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="9">
         <v>1</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="9">
         <v>3</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="9">
         <v>3</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1183,30 +1774,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0A25773-9FA7-469E-9C34-E01D4F42D4B0}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.81640625" customWidth="1"/>
     <col min="2" max="2" width="23.81640625" customWidth="1"/>
     <col min="3" max="3" width="12.453125" customWidth="1"/>
-    <col min="4" max="4" width="48.26953125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="48.26953125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" spans="1:4" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
@@ -1214,277 +1805,271 @@
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:4" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="4">
         <v>2023</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="4">
         <v>56040</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="9">
+      <c r="B8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="4">
         <v>77.875</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="6" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="4">
         <v>245</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="9">
+      <c r="B10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="4">
         <v>10</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="9">
+      <c r="B11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="4">
         <v>32.25</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="9">
+      <c r="B12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="4">
         <v>79.75</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="9">
+      <c r="B13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4">
         <v>1.6</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="9">
+      <c r="B14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="4">
         <v>4.84</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="9">
+      <c r="B15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="4">
         <v>38.5</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="9">
+      <c r="B16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="4">
         <v>125</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="9">
+      <c r="B17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="4">
         <v>7.12</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="9">
+      <c r="B18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="4">
         <v>4.25</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="9">
+      <c r="B19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="4">
         <v>22</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="4">
         <v>60</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="B21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="4">
         <v>78.2</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="6" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="9">
+      <c r="B22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="4">
         <v>74.5</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="6" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1507,20 +2092,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
@@ -1529,238 +2114,238 @@
       <c r="D3" s="16"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="9">
         <v>2025</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="52" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="9" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="52" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="9">
         <v>58286</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="9" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="52" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="117" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="9" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="91" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="9" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="39" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="9">
         <v>4</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="9" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="39" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="18">
+      <c r="B13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="9">
         <v>87.09</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="9" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="39" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="18">
+      <c r="B14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="9">
         <v>22.52</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="9" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="18">
+      <c r="B15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="9">
         <v>0.28000000000000003</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="9" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="52" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="18">
+      <c r="B16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="9">
         <v>0.11</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="18">
+      <c r="B17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="9">
         <v>0.01</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="18">
+      <c r="B18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="9">
         <v>126.08</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="20"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="20"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="11"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="20"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="20"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1768,6 +2353,7 @@
     <mergeCell ref="A2:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1776,27 +2362,27 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" customWidth="1"/>
     <col min="2" max="2" width="24.26953125" customWidth="1"/>
     <col min="3" max="3" width="22.26953125" customWidth="1"/>
     <col min="4" max="4" width="30.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
@@ -1805,174 +2391,174 @@
       <c r="D3" s="16"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="2">
         <v>55867</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="2">
         <v>0</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="2">
         <v>1884</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="2">
         <v>92</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="2" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="2">
         <v>51</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="2" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="2">
         <v>44</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="2" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="2">
         <v>1</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="2" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="2">
         <v>0</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="50" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="2">
         <v>1</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1985,30 +2571,1022 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9CDF3BC-7AB5-415A-847D-2F5855C1FD55}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" customWidth="1"/>
     <col min="2" max="2" width="14.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" customWidth="1"/>
-    <col min="4" max="4" width="27.90625" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="32.08984375" customWidth="1"/>
+    <col min="6" max="6" width="26.36328125" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="11" max="11" width="24.54296875" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" customWidth="1"/>
+    <col min="14" max="14" width="26.08984375" customWidth="1"/>
+    <col min="16" max="16" width="13.36328125" customWidth="1"/>
+    <col min="17" max="17" width="11.6328125" customWidth="1"/>
+    <col min="18" max="18" width="13.453125" customWidth="1"/>
+    <col min="19" max="19" width="23.453125" customWidth="1"/>
+    <col min="21" max="21" width="25.7265625" customWidth="1"/>
+    <col min="24" max="24" width="29.36328125" customWidth="1"/>
+    <col min="26" max="26" width="26.1796875" customWidth="1"/>
+    <col min="28" max="28" width="13.7265625" customWidth="1"/>
+    <col min="29" max="29" width="28.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+    </row>
+    <row r="2" spans="1:29" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A5" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="F5" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="K5" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="P5" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+      <c r="U5" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="V5" s="18"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="18"/>
+      <c r="Z5" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
+      <c r="AC5" s="21"/>
+    </row>
+    <row r="6" spans="1:29" ht="26" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="X6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="52" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="9">
+        <v>2023091801</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0.42370000000000002</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="R7" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W7" s="9">
+        <v>1.835</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA7" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB7" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="52" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="9">
+        <v>56</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0.57630000000000003</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R8" s="9">
+        <v>14</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="U8" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W8" s="9">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="AC8" s="9" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="52" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0.221</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W9" s="9">
+        <v>1</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="52" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="9">
+        <v>55976</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="9">
+        <v>-0.221</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="9">
+        <v>5</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R10" s="9">
+        <v>6.2</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0.19750000000000001</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z10" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="AA10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="9">
+        <v>-8.4589999999999996</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="U11" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="V11" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="W11" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z11" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1.4590000000000001</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="V12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z12" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="AA12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="65" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="U13" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="V13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="W13" s="9">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z13" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="52" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R14" s="9">
+        <v>2.84</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Z14" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="52" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="9">
+        <v>10</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R15" s="9">
+        <v>6.15</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z15" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="AA15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="AC15" s="9" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="65" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z16" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AA16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="AC16" s="9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="M17" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z17" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="AA17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB17" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC17" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="39" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="9">
+        <v>25</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z18" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB18" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC18" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="39" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="13">
+        <v>0.625</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z19" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AA19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB19" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC19" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="52" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z20" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="AA20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB20" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC20" s="9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="26" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="26" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="Z5:AC5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="P5:S5"/>
+    <mergeCell ref="U5:X5"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D4"/>
+    <mergeCell ref="A5:D5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCFFDB7-0F74-45C4-9786-24935BED481C}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.26953125" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="16.90625" customWidth="1"/>
+    <col min="4" max="4" width="25.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="A1" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="A2" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
@@ -2017,248 +3595,411 @@
       <c r="D3" s="16"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
+    <row r="6" spans="1:4" ht="39" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="18">
-        <v>2023091801</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="9">
+        <v>2023090700</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="18">
-        <v>56</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="B7" s="18" t="s">
+      <c r="C7" s="9">
+        <v>59173</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="9">
+        <v>2023</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="18" t="s">
+      <c r="C9" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="18">
-        <v>55976</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="52" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="18" t="s">
+      <c r="C10" s="9">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="39" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B10" s="18" t="s">
+      <c r="C11" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="18">
-        <v>1</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="18">
-        <v>1</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="18">
-        <v>10</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="39" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="39" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="18">
-        <v>25</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A17" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="22">
-        <v>0.625</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="18">
-        <v>0</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A19" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="18">
-        <v>0</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="26" x14ac:dyDescent="0.35">
-      <c r="A20" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>158</v>
-      </c>
+      <c r="C12" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="22"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="A2:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A6099A-4DBE-41FF-81C0-72A4CAC3D69B}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+    </row>
+    <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="9">
+        <v>2024080952</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="9">
+        <v>3379</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="9">
+        <v>57367</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="39" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="9">
+        <v>87.09</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="9">
+        <v>22.52</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.11</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="9">
+        <v>98.51</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="26" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="9">
+        <v>126.08</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="65" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>